--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/08,26/24,08,26 Останкино КИ и ЗПФ/машины Останкино КИ и ЗПФ.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\08,26\24,08,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E414855F-A84F-4999-A8F3-87E3665B2FAF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C94A7A-ACCD-4937-BBBB-8FD111D91B7A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
